--- a/data/manual/Testing.xlsx
+++ b/data/manual/Testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e_edobru\Desktop\Bancomext\Aranceles\data\manual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7144362E-F02A-4901-A0BA-ED7F0CA76875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD69310-AD79-4270-A577-293901C062DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{27A78299-D7C4-4C73-8E12-BDC4991AF799}"/>
   </bookViews>
@@ -16288,24 +16288,24 @@
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A430" t="s">
+      <c r="A430" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="B430">
-        <v>25</v>
-      </c>
-      <c r="C430" t="s">
+      <c r="B430" s="4">
+        <v>25</v>
+      </c>
+      <c r="C430" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A431" t="s">
+      <c r="A431" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="B431">
-        <v>25</v>
-      </c>
-      <c r="C431" t="s">
+      <c r="B431" s="4">
+        <v>25</v>
+      </c>
+      <c r="C431" s="4" t="s">
         <v>861</v>
       </c>
     </row>
@@ -16348,10 +16348,10 @@
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A436" s="1" t="s">
+      <c r="A436" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="B436">
+      <c r="B436" s="4">
         <v>25</v>
       </c>
     </row>
@@ -16378,18 +16378,18 @@
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A439" s="1" t="s">
+      <c r="A439" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="B439">
+      <c r="B439" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A440" s="1" t="s">
+      <c r="A440" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="B440">
+      <c r="B440" s="4">
         <v>25</v>
       </c>
     </row>
@@ -16421,34 +16421,34 @@
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A444" s="1" t="s">
+      <c r="A444" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="B444">
+      <c r="B444" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A445" s="1" t="s">
+      <c r="A445" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="B445">
+      <c r="B445" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A446" s="1" t="s">
+      <c r="A446" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="B446">
+      <c r="B446" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A447" s="1" t="s">
+      <c r="A447" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="B447">
+      <c r="B447" s="4">
         <v>25</v>
       </c>
     </row>
@@ -16469,34 +16469,34 @@
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A450" s="1" t="s">
+      <c r="A450" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="B450">
+      <c r="B450" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A451" s="1" t="s">
+      <c r="A451" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="B451">
+      <c r="B451" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A452" s="1" t="s">
+      <c r="A452" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="B452">
+      <c r="B452" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A453" s="1" t="s">
+      <c r="A453" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="B453">
+      <c r="B453" s="4">
         <v>25</v>
       </c>
     </row>
@@ -16509,4108 +16509,4108 @@
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A455" s="1" t="s">
+      <c r="A455" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="B455">
+      <c r="B455" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A456" s="1" t="s">
+      <c r="A456" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="B456">
+      <c r="B456" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A457" s="1" t="s">
+      <c r="A457" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="B457">
+      <c r="B457" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A458" s="1" t="s">
+      <c r="A458" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="B458">
+      <c r="B458" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A459" s="1" t="s">
+      <c r="A459" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="B459">
+      <c r="B459" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A460" s="1" t="s">
+      <c r="A460" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="B460">
+      <c r="B460" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A461" s="1" t="s">
+      <c r="A461" s="3" t="s">
         <v>638</v>
       </c>
-      <c r="B461" t="s">
+      <c r="B461" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A462" s="1" t="s">
+      <c r="A462" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="B462">
+      <c r="B462" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A463" s="1" t="s">
+      <c r="A463" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="B463">
+      <c r="B463" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A464" t="s">
+      <c r="A464" s="4" t="s">
         <v>720</v>
       </c>
-      <c r="B464">
-        <v>25</v>
-      </c>
-      <c r="C464" t="s">
+      <c r="B464" s="4">
+        <v>25</v>
+      </c>
+      <c r="C464" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A465" t="s">
+      <c r="A465" s="4" t="s">
         <v>721</v>
       </c>
-      <c r="B465">
-        <v>25</v>
-      </c>
-      <c r="C465" t="s">
+      <c r="B465" s="4">
+        <v>25</v>
+      </c>
+      <c r="C465" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A466" t="s">
+      <c r="A466" s="4" t="s">
         <v>722</v>
       </c>
-      <c r="B466">
-        <v>25</v>
-      </c>
-      <c r="C466" t="s">
+      <c r="B466" s="4">
+        <v>25</v>
+      </c>
+      <c r="C466" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A467" t="s">
+      <c r="A467" s="4" t="s">
         <v>723</v>
       </c>
-      <c r="B467">
-        <v>25</v>
-      </c>
-      <c r="C467" t="s">
+      <c r="B467" s="4">
+        <v>25</v>
+      </c>
+      <c r="C467" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A468" t="s">
+      <c r="A468" s="4" t="s">
         <v>869</v>
       </c>
-      <c r="B468">
-        <v>25</v>
-      </c>
-      <c r="C468" t="s">
+      <c r="B468" s="4">
+        <v>25</v>
+      </c>
+      <c r="C468" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A469" t="s">
+      <c r="A469" s="4" t="s">
         <v>870</v>
       </c>
-      <c r="B469">
-        <v>25</v>
-      </c>
-      <c r="C469" t="s">
+      <c r="B469" s="4">
+        <v>25</v>
+      </c>
+      <c r="C469" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A470" t="s">
+      <c r="A470" s="4" t="s">
         <v>871</v>
       </c>
-      <c r="B470">
-        <v>25</v>
-      </c>
-      <c r="C470" t="s">
+      <c r="B470" s="4">
+        <v>25</v>
+      </c>
+      <c r="C470" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A471" t="s">
+      <c r="A471" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="B471">
-        <v>25</v>
-      </c>
-      <c r="C471" t="s">
+      <c r="B471" s="4">
+        <v>25</v>
+      </c>
+      <c r="C471" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A472" t="s">
+      <c r="A472" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="B472">
-        <v>25</v>
-      </c>
-      <c r="C472" t="s">
+      <c r="B472" s="4">
+        <v>25</v>
+      </c>
+      <c r="C472" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A473" t="s">
+      <c r="A473" s="4" t="s">
         <v>874</v>
       </c>
-      <c r="B473">
-        <v>25</v>
-      </c>
-      <c r="C473" t="s">
+      <c r="B473" s="4">
+        <v>25</v>
+      </c>
+      <c r="C473" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A474" s="1" t="s">
+      <c r="A474" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="B474">
+      <c r="B474" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A475" s="1" t="s">
+      <c r="A475" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="B475">
+      <c r="B475" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A476" t="s">
+      <c r="A476" s="4" t="s">
         <v>724</v>
       </c>
-      <c r="B476">
-        <v>25</v>
-      </c>
-      <c r="C476" t="s">
+      <c r="B476" s="4">
+        <v>25</v>
+      </c>
+      <c r="C476" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A477" t="s">
+      <c r="A477" s="4" t="s">
         <v>724</v>
       </c>
-      <c r="B477">
-        <v>25</v>
-      </c>
-      <c r="C477" t="s">
+      <c r="B477" s="4">
+        <v>25</v>
+      </c>
+      <c r="C477" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A478" t="s">
+      <c r="A478" s="4" t="s">
         <v>725</v>
       </c>
-      <c r="B478">
-        <v>25</v>
-      </c>
-      <c r="C478" t="s">
+      <c r="B478" s="4">
+        <v>25</v>
+      </c>
+      <c r="C478" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A479" t="s">
+      <c r="A479" s="4" t="s">
         <v>725</v>
       </c>
-      <c r="B479">
-        <v>25</v>
-      </c>
-      <c r="C479" t="s">
+      <c r="B479" s="4">
+        <v>25</v>
+      </c>
+      <c r="C479" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A480" t="s">
+      <c r="A480" s="4" t="s">
         <v>726</v>
       </c>
-      <c r="B480">
-        <v>25</v>
-      </c>
-      <c r="C480" t="s">
+      <c r="B480" s="4">
+        <v>25</v>
+      </c>
+      <c r="C480" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A481" t="s">
+      <c r="A481" s="4" t="s">
         <v>726</v>
       </c>
-      <c r="B481">
-        <v>25</v>
-      </c>
-      <c r="C481" t="s">
+      <c r="B481" s="4">
+        <v>25</v>
+      </c>
+      <c r="C481" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A482" s="1" t="s">
+      <c r="A482" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="B482">
+      <c r="B482" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A483" s="1" t="s">
+      <c r="A483" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="B483">
+      <c r="B483" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A484" s="1" t="s">
+      <c r="A484" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="B484">
+      <c r="B484" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A485" s="1" t="s">
+      <c r="A485" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="B485">
+      <c r="B485" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A486" s="1" t="s">
+      <c r="A486" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="B486">
+      <c r="B486" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A487" s="1" t="s">
+      <c r="A487" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="B487">
+      <c r="B487" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A488" t="s">
+      <c r="A488" s="4" t="s">
         <v>727</v>
       </c>
-      <c r="B488">
-        <v>25</v>
-      </c>
-      <c r="C488" t="s">
+      <c r="B488" s="4">
+        <v>25</v>
+      </c>
+      <c r="C488" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A489" t="s">
+      <c r="A489" s="4" t="s">
         <v>727</v>
       </c>
-      <c r="B489">
-        <v>25</v>
-      </c>
-      <c r="C489" t="s">
+      <c r="B489" s="4">
+        <v>25</v>
+      </c>
+      <c r="C489" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A490" t="s">
+      <c r="A490" s="4" t="s">
         <v>728</v>
       </c>
-      <c r="B490">
-        <v>25</v>
-      </c>
-      <c r="C490" t="s">
+      <c r="B490" s="4">
+        <v>25</v>
+      </c>
+      <c r="C490" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A491" t="s">
+      <c r="A491" s="4" t="s">
         <v>728</v>
       </c>
-      <c r="B491">
-        <v>25</v>
-      </c>
-      <c r="C491" t="s">
+      <c r="B491" s="4">
+        <v>25</v>
+      </c>
+      <c r="C491" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A492" s="1" t="s">
+      <c r="A492" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="B492">
+      <c r="B492" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A493" t="s">
+      <c r="A493" s="4" t="s">
         <v>729</v>
       </c>
-      <c r="B493">
-        <v>25</v>
-      </c>
-      <c r="C493" t="s">
+      <c r="B493" s="4">
+        <v>25</v>
+      </c>
+      <c r="C493" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A494" t="s">
+      <c r="A494" s="4" t="s">
         <v>729</v>
       </c>
-      <c r="B494">
-        <v>25</v>
-      </c>
-      <c r="C494" t="s">
+      <c r="B494" s="4">
+        <v>25</v>
+      </c>
+      <c r="C494" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A495" t="s">
+      <c r="A495" s="4" t="s">
         <v>730</v>
       </c>
-      <c r="B495">
-        <v>25</v>
-      </c>
-      <c r="C495" t="s">
+      <c r="B495" s="4">
+        <v>25</v>
+      </c>
+      <c r="C495" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A496" t="s">
+      <c r="A496" s="4" t="s">
         <v>730</v>
       </c>
-      <c r="B496">
-        <v>25</v>
-      </c>
-      <c r="C496" t="s">
+      <c r="B496" s="4">
+        <v>25</v>
+      </c>
+      <c r="C496" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A497" s="1" t="s">
+      <c r="A497" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="B497">
+      <c r="B497" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A498" s="1" t="s">
+      <c r="A498" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="B498">
+      <c r="B498" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A499" s="1" t="s">
+      <c r="A499" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="B499">
+      <c r="B499" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A500" s="1" t="s">
+      <c r="A500" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="B500">
+      <c r="B500" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A501" t="s">
+      <c r="A501" s="4" t="s">
         <v>731</v>
       </c>
-      <c r="B501">
-        <v>25</v>
-      </c>
-      <c r="C501" t="s">
+      <c r="B501" s="4">
+        <v>25</v>
+      </c>
+      <c r="C501" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A502" t="s">
+      <c r="A502" s="4" t="s">
         <v>731</v>
       </c>
-      <c r="B502">
-        <v>25</v>
-      </c>
-      <c r="C502" t="s">
+      <c r="B502" s="4">
+        <v>25</v>
+      </c>
+      <c r="C502" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A503" t="s">
+      <c r="A503" s="4" t="s">
         <v>732</v>
       </c>
-      <c r="B503">
-        <v>25</v>
-      </c>
-      <c r="C503" t="s">
+      <c r="B503" s="4">
+        <v>25</v>
+      </c>
+      <c r="C503" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A504" t="s">
+      <c r="A504" s="4" t="s">
         <v>732</v>
       </c>
-      <c r="B504">
-        <v>25</v>
-      </c>
-      <c r="C504" t="s">
+      <c r="B504" s="4">
+        <v>25</v>
+      </c>
+      <c r="C504" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A505" t="s">
+      <c r="A505" s="4" t="s">
         <v>733</v>
       </c>
-      <c r="B505">
-        <v>25</v>
-      </c>
-      <c r="C505" t="s">
+      <c r="B505" s="4">
+        <v>25</v>
+      </c>
+      <c r="C505" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A506" t="s">
+      <c r="A506" s="4" t="s">
         <v>733</v>
       </c>
-      <c r="B506">
-        <v>25</v>
-      </c>
-      <c r="C506" t="s">
+      <c r="B506" s="4">
+        <v>25</v>
+      </c>
+      <c r="C506" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A507" s="1" t="s">
+      <c r="A507" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="B507">
+      <c r="B507" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A508" t="s">
+      <c r="A508" s="4" t="s">
         <v>734</v>
       </c>
-      <c r="B508">
-        <v>25</v>
-      </c>
-      <c r="C508" t="s">
+      <c r="B508" s="4">
+        <v>25</v>
+      </c>
+      <c r="C508" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A509" t="s">
+      <c r="A509" s="4" t="s">
         <v>734</v>
       </c>
-      <c r="B509">
-        <v>25</v>
-      </c>
-      <c r="C509" t="s">
+      <c r="B509" s="4">
+        <v>25</v>
+      </c>
+      <c r="C509" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A510" s="1" t="s">
+      <c r="A510" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="B510">
+      <c r="B510" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A511" s="1" t="s">
+      <c r="A511" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="B511">
+      <c r="B511" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A512" s="1" t="s">
+      <c r="A512" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="B512">
+      <c r="B512" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A513" s="1" t="s">
+      <c r="A513" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="B513">
+      <c r="B513" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A514" s="1" t="s">
+      <c r="A514" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="B514">
+      <c r="B514" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A515" s="1" t="s">
+      <c r="A515" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="B515">
+      <c r="B515" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A516" t="s">
+      <c r="A516" s="4" t="s">
         <v>735</v>
       </c>
-      <c r="B516">
-        <v>25</v>
-      </c>
-      <c r="C516" t="s">
+      <c r="B516" s="4">
+        <v>25</v>
+      </c>
+      <c r="C516" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A517" t="s">
+      <c r="A517" s="4" t="s">
         <v>735</v>
       </c>
-      <c r="B517">
-        <v>25</v>
-      </c>
-      <c r="C517" t="s">
+      <c r="B517" s="4">
+        <v>25</v>
+      </c>
+      <c r="C517" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A518" s="1" t="s">
+      <c r="A518" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="B518">
+      <c r="B518" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A519" s="1" t="s">
+      <c r="A519" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="B519">
+      <c r="B519" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A520" s="1" t="s">
+      <c r="A520" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="B520">
+      <c r="B520" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A521" s="1" t="s">
+      <c r="A521" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="B521">
+      <c r="B521" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A522" s="1" t="s">
+      <c r="A522" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="B522">
+      <c r="B522" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A523" s="1" t="s">
+      <c r="A523" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="B523">
+      <c r="B523" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A524" s="1" t="s">
+      <c r="A524" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="B524">
+      <c r="B524" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A525" s="1" t="s">
+      <c r="A525" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="B525">
+      <c r="B525" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A526" s="1" t="s">
+      <c r="A526" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="B526">
+      <c r="B526" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A527" s="1" t="s">
+      <c r="A527" s="3" t="s">
         <v>639</v>
       </c>
-      <c r="B527" t="s">
+      <c r="B527" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A528" s="1" t="s">
+      <c r="A528" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="B528">
+      <c r="B528" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A529" s="1" t="s">
+      <c r="A529" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="B529">
+      <c r="B529" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A530" s="1" t="s">
+      <c r="A530" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="B530">
+      <c r="B530" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A531" s="1" t="s">
+      <c r="A531" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="B531">
+      <c r="B531" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A532" s="1" t="s">
+      <c r="A532" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="B532">
+      <c r="B532" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A533" s="1" t="s">
+      <c r="A533" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B533">
+      <c r="B533" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A534" s="1" t="s">
+      <c r="A534" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="B534">
+      <c r="B534" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A535" s="1" t="s">
+      <c r="A535" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="B535">
+      <c r="B535" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A536" s="1" t="s">
+      <c r="A536" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="B536">
+      <c r="B536" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A537" s="1" t="s">
+      <c r="A537" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="B537">
+      <c r="B537" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A538" s="1" t="s">
+      <c r="A538" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="B538">
+      <c r="B538" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A539" s="1" t="s">
+      <c r="A539" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="B539">
+      <c r="B539" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A540" s="1" t="s">
+      <c r="A540" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="B540">
+      <c r="B540" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A541" t="s">
+      <c r="A541" s="4" t="s">
         <v>736</v>
       </c>
-      <c r="B541">
-        <v>25</v>
-      </c>
-      <c r="C541" t="s">
+      <c r="B541" s="4">
+        <v>25</v>
+      </c>
+      <c r="C541" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A542" t="s">
+      <c r="A542" s="4" t="s">
         <v>736</v>
       </c>
-      <c r="B542">
-        <v>25</v>
-      </c>
-      <c r="C542" t="s">
+      <c r="B542" s="4">
+        <v>25</v>
+      </c>
+      <c r="C542" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A543" s="1" t="s">
+      <c r="A543" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="B543" t="s">
+      <c r="B543" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A544" t="s">
+      <c r="A544" s="4" t="s">
         <v>737</v>
       </c>
-      <c r="B544">
-        <v>25</v>
-      </c>
-      <c r="C544" t="s">
+      <c r="B544" s="4">
+        <v>25</v>
+      </c>
+      <c r="C544" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A545" t="s">
+      <c r="A545" s="4" t="s">
         <v>737</v>
       </c>
-      <c r="B545">
-        <v>25</v>
-      </c>
-      <c r="C545" t="s">
+      <c r="B545" s="4">
+        <v>25</v>
+      </c>
+      <c r="C545" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A546" s="1" t="s">
+      <c r="A546" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="B546">
+      <c r="B546" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A547" s="1" t="s">
+      <c r="A547" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="B547">
+      <c r="B547" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A548" s="1" t="s">
+      <c r="A548" s="3" t="s">
         <v>641</v>
       </c>
-      <c r="B548" t="s">
+      <c r="B548" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A549" s="1" t="s">
+      <c r="A549" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="B549">
+      <c r="B549" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A550" s="1" t="s">
+      <c r="A550" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="B550">
+      <c r="B550" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A551" t="s">
+      <c r="A551" s="4" t="s">
         <v>738</v>
       </c>
-      <c r="B551">
-        <v>25</v>
-      </c>
-      <c r="C551" t="s">
+      <c r="B551" s="4">
+        <v>25</v>
+      </c>
+      <c r="C551" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A552" t="s">
+      <c r="A552" s="4" t="s">
         <v>738</v>
       </c>
-      <c r="B552">
-        <v>25</v>
-      </c>
-      <c r="C552" t="s">
+      <c r="B552" s="4">
+        <v>25</v>
+      </c>
+      <c r="C552" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A553" s="1" t="s">
+      <c r="A553" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="B553">
+      <c r="B553" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A554" s="1" t="s">
+      <c r="A554" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="B554">
+      <c r="B554" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A555" t="s">
+      <c r="A555" s="4" t="s">
         <v>739</v>
       </c>
-      <c r="B555">
-        <v>25</v>
-      </c>
-      <c r="C555" t="s">
+      <c r="B555" s="4">
+        <v>25</v>
+      </c>
+      <c r="C555" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A556" t="s">
+      <c r="A556" s="4" t="s">
         <v>739</v>
       </c>
-      <c r="B556">
-        <v>25</v>
-      </c>
-      <c r="C556" t="s">
+      <c r="B556" s="4">
+        <v>25</v>
+      </c>
+      <c r="C556" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A557" s="1" t="s">
+      <c r="A557" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="B557">
+      <c r="B557" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A558" s="1" t="s">
+      <c r="A558" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="B558">
+      <c r="B558" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A559" s="1" t="s">
+      <c r="A559" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="B559">
+      <c r="B559" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A560" s="1" t="s">
+      <c r="A560" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="B560">
+      <c r="B560" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A561" s="1" t="s">
+      <c r="A561" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="B561">
+      <c r="B561" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A562" s="1" t="s">
+      <c r="A562" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="B562">
+      <c r="B562" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A563" s="1" t="s">
+      <c r="A563" s="3" t="s">
         <v>642</v>
       </c>
-      <c r="B563" t="s">
+      <c r="B563" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A564" s="1" t="s">
+      <c r="A564" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="B564" t="s">
+      <c r="B564" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A565" s="1" t="s">
+      <c r="A565" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="B565" t="s">
+      <c r="B565" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A566" s="1" t="s">
+      <c r="A566" s="3" t="s">
         <v>645</v>
       </c>
-      <c r="B566" t="s">
+      <c r="B566" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A567" s="1" t="s">
+      <c r="A567" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="B567" t="s">
+      <c r="B567" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A568" s="1" t="s">
+      <c r="A568" s="3" t="s">
         <v>647</v>
       </c>
-      <c r="B568" t="s">
+      <c r="B568" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A569" s="1" t="s">
+      <c r="A569" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="B569">
+      <c r="B569" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A570" s="1" t="s">
+      <c r="A570" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="B570">
+      <c r="B570" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A571" s="1" t="s">
+      <c r="A571" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="B571">
+      <c r="B571" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A572" s="1" t="s">
+      <c r="A572" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="B572">
+      <c r="B572" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A573" s="1" t="s">
+      <c r="A573" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="B573">
+      <c r="B573" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A574" s="1" t="s">
+      <c r="A574" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="B574">
+      <c r="B574" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A575" s="1" t="s">
+      <c r="A575" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="B575">
+      <c r="B575" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A576" s="1" t="s">
+      <c r="A576" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="B576">
+      <c r="B576" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A577" s="1" t="s">
+      <c r="A577" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="B577">
+      <c r="B577" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A578" s="1" t="s">
+      <c r="A578" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="B578">
+      <c r="B578" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A579" s="1" t="s">
+      <c r="A579" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="B579">
+      <c r="B579" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A580" t="s">
+      <c r="A580" s="4" t="s">
         <v>740</v>
       </c>
-      <c r="B580">
-        <v>25</v>
-      </c>
-      <c r="C580" t="s">
+      <c r="B580" s="4">
+        <v>25</v>
+      </c>
+      <c r="C580" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A581" t="s">
+      <c r="A581" s="4" t="s">
         <v>740</v>
       </c>
-      <c r="B581">
-        <v>25</v>
-      </c>
-      <c r="C581" t="s">
+      <c r="B581" s="4">
+        <v>25</v>
+      </c>
+      <c r="C581" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A582" s="1" t="s">
+      <c r="A582" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="B582">
+      <c r="B582" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A583" s="1" t="s">
+      <c r="A583" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="B583">
+      <c r="B583" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A584" s="1" t="s">
+      <c r="A584" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="B584" t="s">
+      <c r="B584" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A585" s="1" t="s">
+      <c r="A585" s="3" t="s">
         <v>649</v>
       </c>
-      <c r="B585" t="s">
+      <c r="B585" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A586" s="1" t="s">
+      <c r="A586" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="B586">
+      <c r="B586" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A587" s="1" t="s">
+      <c r="A587" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="B587">
+      <c r="B587" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A588" s="1" t="s">
+      <c r="A588" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="B588">
+      <c r="B588" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A589" s="1" t="s">
+      <c r="A589" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="B589">
+      <c r="B589" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A590" s="1" t="s">
+      <c r="A590" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="B590">
+      <c r="B590" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A591" s="1" t="s">
+      <c r="A591" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="B591">
+      <c r="B591" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A592" s="1" t="s">
+      <c r="A592" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="B592">
+      <c r="B592" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A593" s="1" t="s">
+      <c r="A593" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="B593">
+      <c r="B593" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A594" s="1" t="s">
+      <c r="A594" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="B594">
+      <c r="B594" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A595" s="1" t="s">
+      <c r="A595" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="B595">
+      <c r="B595" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A596" s="1" t="s">
+      <c r="A596" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="B596">
+      <c r="B596" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A597" s="1" t="s">
+      <c r="A597" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="B597">
+      <c r="B597" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A598" s="1" t="s">
+      <c r="A598" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="B598">
+      <c r="B598" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A599" s="1" t="s">
+      <c r="A599" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="B599">
+      <c r="B599" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A600" s="1" t="s">
+      <c r="A600" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="B600">
+      <c r="B600" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A601" s="1" t="s">
+      <c r="A601" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="B601">
+      <c r="B601" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A602" s="1" t="s">
+      <c r="A602" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="B602">
+      <c r="B602" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A603" s="1" t="s">
+      <c r="A603" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="B603">
+      <c r="B603" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A604" s="1" t="s">
+      <c r="A604" s="3" t="s">
         <v>650</v>
       </c>
-      <c r="B604" t="s">
+      <c r="B604" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A605" s="1" t="s">
+      <c r="A605" s="3" t="s">
         <v>651</v>
       </c>
-      <c r="B605" t="s">
+      <c r="B605" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A606" s="1" t="s">
+      <c r="A606" s="3" t="s">
         <v>652</v>
       </c>
-      <c r="B606" t="s">
+      <c r="B606" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A607" s="1" t="s">
+      <c r="A607" s="3" t="s">
         <v>653</v>
       </c>
-      <c r="B607" t="s">
+      <c r="B607" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A608" s="1" t="s">
+      <c r="A608" s="3" t="s">
         <v>654</v>
       </c>
-      <c r="B608" t="s">
+      <c r="B608" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A609" s="1" t="s">
+      <c r="A609" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="B609" t="s">
+      <c r="B609" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A610" s="1" t="s">
+      <c r="A610" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="B610">
+      <c r="B610" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A611" s="1" t="s">
+      <c r="A611" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="B611">
+      <c r="B611" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A612" s="1" t="s">
+      <c r="A612" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="B612">
+      <c r="B612" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A613" s="1" t="s">
+      <c r="A613" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="B613">
+      <c r="B613" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A614" t="s">
+      <c r="A614" s="4" t="s">
         <v>741</v>
       </c>
-      <c r="B614">
-        <v>25</v>
-      </c>
-      <c r="C614" t="s">
+      <c r="B614" s="4">
+        <v>25</v>
+      </c>
+      <c r="C614" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A615" t="s">
+      <c r="A615" s="4" t="s">
         <v>982</v>
       </c>
-      <c r="B615">
-        <v>25</v>
-      </c>
-      <c r="C615" t="s">
+      <c r="B615" s="4">
+        <v>25</v>
+      </c>
+      <c r="C615" s="4" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A616" t="s">
+      <c r="A616" s="4" t="s">
         <v>983</v>
       </c>
-      <c r="B616">
-        <v>25</v>
-      </c>
-      <c r="C616" t="s">
+      <c r="B616" s="4">
+        <v>25</v>
+      </c>
+      <c r="C616" s="4" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A617" t="s">
+      <c r="A617" s="4" t="s">
         <v>984</v>
       </c>
-      <c r="B617">
-        <v>25</v>
-      </c>
-      <c r="C617" t="s">
+      <c r="B617" s="4">
+        <v>25</v>
+      </c>
+      <c r="C617" s="4" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A618" s="1" t="s">
+      <c r="A618" s="3" t="s">
         <v>656</v>
       </c>
-      <c r="B618" t="s">
+      <c r="B618" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A619" s="1" t="s">
+      <c r="A619" s="3" t="s">
         <v>657</v>
       </c>
-      <c r="B619" t="s">
+      <c r="B619" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A620" s="1" t="s">
+      <c r="A620" s="3" t="s">
         <v>658</v>
       </c>
-      <c r="B620" t="s">
+      <c r="B620" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A621" s="1" t="s">
+      <c r="A621" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="B621" t="s">
+      <c r="B621" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A622" s="1" t="s">
+      <c r="A622" s="3" t="s">
         <v>660</v>
       </c>
-      <c r="B622" t="s">
+      <c r="B622" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A623" s="1" t="s">
+      <c r="A623" s="3" t="s">
         <v>661</v>
       </c>
-      <c r="B623" t="s">
+      <c r="B623" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A624" s="1" t="s">
+      <c r="A624" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="B624">
+      <c r="B624" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A625" s="1" t="s">
+      <c r="A625" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="B625">
+      <c r="B625" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A626" s="1" t="s">
+      <c r="A626" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="B626" t="s">
+      <c r="B626" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A627" s="1" t="s">
+      <c r="A627" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="B627">
+      <c r="B627" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A628" s="1" t="s">
+      <c r="A628" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="B628">
+      <c r="B628" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A629" s="1" t="s">
+      <c r="A629" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="B629">
+      <c r="B629" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A630" s="1" t="s">
+      <c r="A630" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="B630">
+      <c r="B630" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A631" s="1" t="s">
+      <c r="A631" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="B631">
+      <c r="B631" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A632" s="1" t="s">
+      <c r="A632" s="3" t="s">
         <v>662</v>
       </c>
-      <c r="B632" t="s">
+      <c r="B632" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A633" s="1" t="s">
+      <c r="A633" s="3" t="s">
         <v>671</v>
       </c>
-      <c r="B633" t="s">
+      <c r="B633" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A634" s="1" t="s">
+      <c r="A634" s="3" t="s">
         <v>663</v>
       </c>
-      <c r="B634" t="s">
+      <c r="B634" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A635" s="1" t="s">
+      <c r="A635" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="B635" t="s">
+      <c r="B635" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A636" s="1" t="s">
+      <c r="A636" s="3" t="s">
         <v>665</v>
       </c>
-      <c r="B636" t="s">
+      <c r="B636" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A637" s="1" t="s">
+      <c r="A637" s="3" t="s">
         <v>666</v>
       </c>
-      <c r="B637" t="s">
+      <c r="B637" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A638" s="1" t="s">
+      <c r="A638" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="B638">
+      <c r="B638" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A639" s="1" t="s">
+      <c r="A639" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="B639">
+      <c r="B639" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A640" t="s">
+      <c r="A640" s="4" t="s">
         <v>742</v>
       </c>
-      <c r="B640">
-        <v>25</v>
-      </c>
-      <c r="C640" t="s">
+      <c r="B640" s="4">
+        <v>25</v>
+      </c>
+      <c r="C640" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A641" t="s">
+      <c r="A641" s="4" t="s">
         <v>742</v>
       </c>
-      <c r="B641">
-        <v>25</v>
-      </c>
-      <c r="C641" t="s">
+      <c r="B641" s="4">
+        <v>25</v>
+      </c>
+      <c r="C641" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A642" s="1" t="s">
+      <c r="A642" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="B642">
+      <c r="B642" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A643" s="1" t="s">
+      <c r="A643" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="B643">
+      <c r="B643" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A644" s="1" t="s">
+      <c r="A644" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="B644">
+      <c r="B644" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A645" s="1" t="s">
+      <c r="A645" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="B645">
+      <c r="B645" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A646" s="1" t="s">
+      <c r="A646" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="B646">
+      <c r="B646" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A647" s="1" t="s">
+      <c r="A647" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="B647">
+      <c r="B647" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A648" s="1" t="s">
+      <c r="A648" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="B648">
+      <c r="B648" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A649" s="1" t="s">
+      <c r="A649" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="B649">
+      <c r="B649" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A650" t="s">
+      <c r="A650" s="4" t="s">
         <v>743</v>
       </c>
-      <c r="B650">
-        <v>25</v>
-      </c>
-      <c r="C650" t="s">
+      <c r="B650" s="4">
+        <v>25</v>
+      </c>
+      <c r="C650" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A651" t="s">
+      <c r="A651" s="4" t="s">
         <v>743</v>
       </c>
-      <c r="B651">
-        <v>25</v>
-      </c>
-      <c r="C651" t="s">
+      <c r="B651" s="4">
+        <v>25</v>
+      </c>
+      <c r="C651" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A652" t="s">
+      <c r="A652" s="4" t="s">
         <v>744</v>
       </c>
-      <c r="B652">
-        <v>25</v>
-      </c>
-      <c r="C652" t="s">
+      <c r="B652" s="4">
+        <v>25</v>
+      </c>
+      <c r="C652" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A653" t="s">
+      <c r="A653" s="4" t="s">
         <v>744</v>
       </c>
-      <c r="B653">
-        <v>25</v>
-      </c>
-      <c r="C653" t="s">
+      <c r="B653" s="4">
+        <v>25</v>
+      </c>
+      <c r="C653" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A654" s="1" t="s">
+      <c r="A654" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="B654">
+      <c r="B654" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A655" s="1" t="s">
+      <c r="A655" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="B655">
+      <c r="B655" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A656" s="1" t="s">
+      <c r="A656" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="B656">
+      <c r="B656" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A657" s="1" t="s">
+      <c r="A657" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="B657">
+      <c r="B657" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A658" s="1" t="s">
+      <c r="A658" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="B658">
+      <c r="B658" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A659" t="s">
+      <c r="A659" s="4" t="s">
         <v>745</v>
       </c>
-      <c r="B659">
-        <v>25</v>
-      </c>
-      <c r="C659" t="s">
+      <c r="B659" s="4">
+        <v>25</v>
+      </c>
+      <c r="C659" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A660" t="s">
+      <c r="A660" s="4" t="s">
         <v>745</v>
       </c>
-      <c r="B660">
-        <v>25</v>
-      </c>
-      <c r="C660" t="s">
+      <c r="B660" s="4">
+        <v>25</v>
+      </c>
+      <c r="C660" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A661" t="s">
+      <c r="A661" s="4" t="s">
         <v>746</v>
       </c>
-      <c r="B661">
-        <v>25</v>
-      </c>
-      <c r="C661" t="s">
+      <c r="B661" s="4">
+        <v>25</v>
+      </c>
+      <c r="C661" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A662" t="s">
+      <c r="A662" s="4" t="s">
         <v>746</v>
       </c>
-      <c r="B662">
-        <v>25</v>
-      </c>
-      <c r="C662" t="s">
+      <c r="B662" s="4">
+        <v>25</v>
+      </c>
+      <c r="C662" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A663" t="s">
+      <c r="A663" s="4" t="s">
         <v>747</v>
       </c>
-      <c r="B663">
-        <v>25</v>
-      </c>
-      <c r="C663" t="s">
+      <c r="B663" s="4">
+        <v>25</v>
+      </c>
+      <c r="C663" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A664" t="s">
+      <c r="A664" s="4" t="s">
         <v>747</v>
       </c>
-      <c r="B664">
-        <v>25</v>
-      </c>
-      <c r="C664" t="s">
+      <c r="B664" s="4">
+        <v>25</v>
+      </c>
+      <c r="C664" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A665" t="s">
+      <c r="A665" s="4" t="s">
         <v>748</v>
       </c>
-      <c r="B665">
-        <v>25</v>
-      </c>
-      <c r="C665" t="s">
+      <c r="B665" s="4">
+        <v>25</v>
+      </c>
+      <c r="C665" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A666" t="s">
+      <c r="A666" s="4" t="s">
         <v>748</v>
       </c>
-      <c r="B666">
-        <v>25</v>
-      </c>
-      <c r="C666" t="s">
+      <c r="B666" s="4">
+        <v>25</v>
+      </c>
+      <c r="C666" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A667" s="1" t="s">
+      <c r="A667" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="B667">
+      <c r="B667" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A668" s="1" t="s">
+      <c r="A668" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="B668">
+      <c r="B668" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A669" t="s">
+      <c r="A669" s="4" t="s">
         <v>749</v>
       </c>
-      <c r="B669">
-        <v>25</v>
-      </c>
-      <c r="C669" t="s">
+      <c r="B669" s="4">
+        <v>25</v>
+      </c>
+      <c r="C669" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A670" t="s">
+      <c r="A670" s="4" t="s">
         <v>749</v>
       </c>
-      <c r="B670">
-        <v>25</v>
-      </c>
-      <c r="C670" t="s">
+      <c r="B670" s="4">
+        <v>25</v>
+      </c>
+      <c r="C670" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A671" t="s">
+      <c r="A671" s="4" t="s">
         <v>750</v>
       </c>
-      <c r="B671">
-        <v>25</v>
-      </c>
-      <c r="C671" t="s">
+      <c r="B671" s="4">
+        <v>25</v>
+      </c>
+      <c r="C671" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A672" t="s">
+      <c r="A672" s="4" t="s">
         <v>750</v>
       </c>
-      <c r="B672">
-        <v>25</v>
-      </c>
-      <c r="C672" t="s">
+      <c r="B672" s="4">
+        <v>25</v>
+      </c>
+      <c r="C672" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A673" s="1" t="s">
+      <c r="A673" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="B673">
+      <c r="B673" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A674" t="s">
+      <c r="A674" s="4" t="s">
         <v>751</v>
       </c>
-      <c r="B674">
-        <v>25</v>
-      </c>
-      <c r="C674" t="s">
+      <c r="B674" s="4">
+        <v>25</v>
+      </c>
+      <c r="C674" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A675" t="s">
+      <c r="A675" s="4" t="s">
         <v>751</v>
       </c>
-      <c r="B675">
-        <v>25</v>
-      </c>
-      <c r="C675" t="s">
+      <c r="B675" s="4">
+        <v>25</v>
+      </c>
+      <c r="C675" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A676" t="s">
+      <c r="A676" s="4" t="s">
         <v>752</v>
       </c>
-      <c r="B676">
-        <v>25</v>
-      </c>
-      <c r="C676" t="s">
+      <c r="B676" s="4">
+        <v>25</v>
+      </c>
+      <c r="C676" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A677" t="s">
+      <c r="A677" s="4" t="s">
         <v>752</v>
       </c>
-      <c r="B677">
-        <v>25</v>
-      </c>
-      <c r="C677" t="s">
+      <c r="B677" s="4">
+        <v>25</v>
+      </c>
+      <c r="C677" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A678" s="1" t="s">
+      <c r="A678" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="B678">
+      <c r="B678" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A679" s="1" t="s">
+      <c r="A679" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="B679">
+      <c r="B679" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A680" s="1" t="s">
+      <c r="A680" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="B680">
+      <c r="B680" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A681" s="1" t="s">
+      <c r="A681" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="B681">
+      <c r="B681" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A682" s="1" t="s">
+      <c r="A682" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="B682">
+      <c r="B682" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A683" s="1" t="s">
+      <c r="A683" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="B683">
+      <c r="B683" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A684" t="s">
+      <c r="A684" s="4" t="s">
         <v>875</v>
       </c>
-      <c r="B684">
-        <v>25</v>
-      </c>
-      <c r="C684" t="s">
+      <c r="B684" s="4">
+        <v>25</v>
+      </c>
+      <c r="C684" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A685" s="1" t="s">
+      <c r="A685" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="B685">
+      <c r="B685" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A686" t="s">
+      <c r="A686" s="4" t="s">
         <v>753</v>
       </c>
-      <c r="B686">
-        <v>25</v>
-      </c>
-      <c r="C686" t="s">
+      <c r="B686" s="4">
+        <v>25</v>
+      </c>
+      <c r="C686" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A687" s="1" t="s">
+      <c r="A687" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="B687">
+      <c r="B687" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A688" t="s">
+      <c r="A688" s="4" t="s">
         <v>754</v>
       </c>
-      <c r="B688">
-        <v>25</v>
-      </c>
-      <c r="C688" t="s">
+      <c r="B688" s="4">
+        <v>25</v>
+      </c>
+      <c r="C688" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A689" s="1" t="s">
+      <c r="A689" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="B689">
+      <c r="B689" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A690" s="1" t="s">
+      <c r="A690" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="B690">
+      <c r="B690" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A691" s="1" t="s">
+      <c r="A691" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="B691">
+      <c r="B691" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A692" s="1" t="s">
+      <c r="A692" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="B692">
+      <c r="B692" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A693" s="1" t="s">
+      <c r="A693" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="B693">
+      <c r="B693" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A694" s="1" t="s">
+      <c r="A694" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="B694">
+      <c r="B694" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A695" s="1" t="s">
+      <c r="A695" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="B695">
+      <c r="B695" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A696" s="1" t="s">
+      <c r="A696" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="B696">
+      <c r="B696" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A697" s="1" t="s">
+      <c r="A697" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="B697">
+      <c r="B697" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A698" s="1" t="s">
+      <c r="A698" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="B698">
+      <c r="B698" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A699" s="1" t="s">
+      <c r="A699" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="B699">
+      <c r="B699" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A700" s="1" t="s">
+      <c r="A700" s="3" t="s">
         <v>667</v>
       </c>
-      <c r="B700" t="s">
+      <c r="B700" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A701" s="1" t="s">
+      <c r="A701" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="B701" t="s">
+      <c r="B701" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A702" s="1" t="s">
+      <c r="A702" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="B702">
+      <c r="B702" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A703" s="1" t="s">
+      <c r="A703" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="B703">
+      <c r="B703" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A704" s="1" t="s">
+      <c r="A704" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="B704">
+      <c r="B704" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="705" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A705" s="1" t="s">
+      <c r="A705" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="B705">
+      <c r="B705" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A706" s="1" t="s">
+      <c r="A706" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="B706">
+      <c r="B706" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="707" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A707" s="1" t="s">
+      <c r="A707" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="B707">
+      <c r="B707" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="708" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A708" t="s">
+      <c r="A708" s="4" t="s">
         <v>755</v>
       </c>
-      <c r="B708">
-        <v>25</v>
-      </c>
-      <c r="C708" t="s">
+      <c r="B708" s="4">
+        <v>25</v>
+      </c>
+      <c r="C708" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="709" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A709" t="s">
+      <c r="A709" s="4" t="s">
         <v>876</v>
       </c>
-      <c r="B709">
-        <v>25</v>
-      </c>
-      <c r="C709" t="s">
+      <c r="B709" s="4">
+        <v>25</v>
+      </c>
+      <c r="C709" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="710" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A710" t="s">
+      <c r="A710" s="4" t="s">
         <v>877</v>
       </c>
-      <c r="B710">
-        <v>25</v>
-      </c>
-      <c r="C710" t="s">
+      <c r="B710" s="4">
+        <v>25</v>
+      </c>
+      <c r="C710" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="711" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A711" t="s">
+      <c r="A711" s="4" t="s">
         <v>878</v>
       </c>
-      <c r="B711">
-        <v>25</v>
-      </c>
-      <c r="C711" t="s">
+      <c r="B711" s="4">
+        <v>25</v>
+      </c>
+      <c r="C711" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="712" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A712" t="s">
+      <c r="A712" s="4" t="s">
         <v>756</v>
       </c>
-      <c r="B712">
-        <v>25</v>
-      </c>
-      <c r="C712" t="s">
+      <c r="B712" s="4">
+        <v>25</v>
+      </c>
+      <c r="C712" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="713" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A713" t="s">
+      <c r="A713" s="4" t="s">
         <v>879</v>
       </c>
-      <c r="B713">
-        <v>25</v>
-      </c>
-      <c r="C713" t="s">
+      <c r="B713" s="4">
+        <v>25</v>
+      </c>
+      <c r="C713" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="714" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A714" t="s">
+      <c r="A714" s="4" t="s">
         <v>880</v>
       </c>
-      <c r="B714">
-        <v>25</v>
-      </c>
-      <c r="C714" t="s">
+      <c r="B714" s="4">
+        <v>25</v>
+      </c>
+      <c r="C714" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A715" t="s">
+      <c r="A715" s="4" t="s">
         <v>881</v>
       </c>
-      <c r="B715">
-        <v>25</v>
-      </c>
-      <c r="C715" t="s">
+      <c r="B715" s="4">
+        <v>25</v>
+      </c>
+      <c r="C715" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="716" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A716" t="s">
+      <c r="A716" s="4" t="s">
         <v>882</v>
       </c>
-      <c r="B716">
-        <v>25</v>
-      </c>
-      <c r="C716" t="s">
+      <c r="B716" s="4">
+        <v>25</v>
+      </c>
+      <c r="C716" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A717" t="s">
+      <c r="A717" s="4" t="s">
         <v>757</v>
       </c>
-      <c r="B717">
-        <v>25</v>
-      </c>
-      <c r="C717" t="s">
+      <c r="B717" s="4">
+        <v>25</v>
+      </c>
+      <c r="C717" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="718" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A718" t="s">
+      <c r="A718" s="4" t="s">
         <v>883</v>
       </c>
-      <c r="B718">
-        <v>25</v>
-      </c>
-      <c r="C718" t="s">
+      <c r="B718" s="4">
+        <v>25</v>
+      </c>
+      <c r="C718" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="719" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A719" t="s">
+      <c r="A719" s="4" t="s">
         <v>884</v>
       </c>
-      <c r="B719">
-        <v>25</v>
-      </c>
-      <c r="C719" t="s">
+      <c r="B719" s="4">
+        <v>25</v>
+      </c>
+      <c r="C719" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="720" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A720" t="s">
+      <c r="A720" s="4" t="s">
         <v>758</v>
       </c>
-      <c r="B720">
-        <v>25</v>
-      </c>
-      <c r="C720" t="s">
+      <c r="B720" s="4">
+        <v>25</v>
+      </c>
+      <c r="C720" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="721" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A721" t="s">
+      <c r="A721" s="4" t="s">
         <v>885</v>
       </c>
-      <c r="B721">
-        <v>25</v>
-      </c>
-      <c r="C721" t="s">
+      <c r="B721" s="4">
+        <v>25</v>
+      </c>
+      <c r="C721" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="722" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A722" t="s">
+      <c r="A722" s="4" t="s">
         <v>886</v>
       </c>
-      <c r="B722">
-        <v>25</v>
-      </c>
-      <c r="C722" t="s">
+      <c r="B722" s="4">
+        <v>25</v>
+      </c>
+      <c r="C722" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="723" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A723" t="s">
+      <c r="A723" s="4" t="s">
         <v>887</v>
       </c>
-      <c r="B723">
-        <v>25</v>
-      </c>
-      <c r="C723" t="s">
+      <c r="B723" s="4">
+        <v>25</v>
+      </c>
+      <c r="C723" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="724" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A724" t="s">
+      <c r="A724" s="4" t="s">
         <v>888</v>
       </c>
-      <c r="B724">
-        <v>25</v>
-      </c>
-      <c r="C724" t="s">
+      <c r="B724" s="4">
+        <v>25</v>
+      </c>
+      <c r="C724" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="725" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A725" t="s">
+      <c r="A725" s="4" t="s">
         <v>759</v>
       </c>
-      <c r="B725">
-        <v>25</v>
-      </c>
-      <c r="C725" t="s">
+      <c r="B725" s="4">
+        <v>25</v>
+      </c>
+      <c r="C725" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="726" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A726" t="s">
+      <c r="A726" s="4" t="s">
         <v>889</v>
       </c>
-      <c r="B726">
-        <v>25</v>
-      </c>
-      <c r="C726" t="s">
+      <c r="B726" s="4">
+        <v>25</v>
+      </c>
+      <c r="C726" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="727" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A727" t="s">
+      <c r="A727" s="4" t="s">
         <v>890</v>
       </c>
-      <c r="B727">
-        <v>25</v>
-      </c>
-      <c r="C727" t="s">
+      <c r="B727" s="4">
+        <v>25</v>
+      </c>
+      <c r="C727" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A728" t="s">
+      <c r="A728" s="4" t="s">
         <v>891</v>
       </c>
-      <c r="B728">
-        <v>25</v>
-      </c>
-      <c r="C728" t="s">
+      <c r="B728" s="4">
+        <v>25</v>
+      </c>
+      <c r="C728" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="729" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A729" t="s">
+      <c r="A729" s="4" t="s">
         <v>892</v>
       </c>
-      <c r="B729">
-        <v>25</v>
-      </c>
-      <c r="C729" t="s">
+      <c r="B729" s="4">
+        <v>25</v>
+      </c>
+      <c r="C729" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="730" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A730" t="s">
+      <c r="A730" s="4" t="s">
         <v>760</v>
       </c>
-      <c r="B730">
-        <v>25</v>
-      </c>
-      <c r="C730" t="s">
+      <c r="B730" s="4">
+        <v>25</v>
+      </c>
+      <c r="C730" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="731" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A731" t="s">
+      <c r="A731" s="4" t="s">
         <v>893</v>
       </c>
-      <c r="B731">
-        <v>25</v>
-      </c>
-      <c r="C731" t="s">
+      <c r="B731" s="4">
+        <v>25</v>
+      </c>
+      <c r="C731" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="732" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A732" t="s">
+      <c r="A732" s="4" t="s">
         <v>894</v>
       </c>
-      <c r="B732">
-        <v>25</v>
-      </c>
-      <c r="C732" t="s">
+      <c r="B732" s="4">
+        <v>25</v>
+      </c>
+      <c r="C732" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="733" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A733" s="1" t="s">
+      <c r="A733" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="B733">
+      <c r="B733" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="734" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A734" s="1" t="s">
+      <c r="A734" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="B734">
+      <c r="B734" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="735" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A735" s="1" t="s">
+      <c r="A735" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="B735">
+      <c r="B735" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="736" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A736" s="1" t="s">
+      <c r="A736" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="B736">
+      <c r="B736" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A737" s="1" t="s">
+      <c r="A737" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="B737">
+      <c r="B737" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A738" s="1" t="s">
+      <c r="A738" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="B738">
+      <c r="B738" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A739" s="1" t="s">
+      <c r="A739" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="B739">
+      <c r="B739" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A740" s="1" t="s">
+      <c r="A740" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="B740">
+      <c r="B740" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A741" s="1" t="s">
+      <c r="A741" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="B741">
+      <c r="B741" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A742" s="1" t="s">
+      <c r="A742" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="B742">
+      <c r="B742" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A743" s="1" t="s">
+      <c r="A743" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="B743">
+      <c r="B743" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A744" s="1" t="s">
+      <c r="A744" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="B744">
+      <c r="B744" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A745" s="1" t="s">
+      <c r="A745" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="B745">
+      <c r="B745" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A746" s="1" t="s">
+      <c r="A746" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="B746">
+      <c r="B746" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A747" s="1" t="s">
+      <c r="A747" s="3" t="s">
         <v>669</v>
       </c>
-      <c r="B747" t="s">
+      <c r="B747" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A748" s="1" t="s">
+      <c r="A748" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="B748">
+      <c r="B748" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A749" s="1" t="s">
+      <c r="A749" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="B749">
+      <c r="B749" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A750" s="1" t="s">
+      <c r="A750" s="3" t="s">
         <v>605</v>
       </c>
-      <c r="B750">
+      <c r="B750" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A751" s="1" t="s">
+      <c r="A751" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="B751">
+      <c r="B751" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A752" s="1" t="s">
+      <c r="A752" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="B752">
+      <c r="B752" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="753" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A753" s="1" t="s">
+      <c r="A753" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="B753" t="s">
+      <c r="B753" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="754" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A754" s="1" t="s">
+      <c r="A754" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="B754" t="s">
+      <c r="B754" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="755" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A755" s="1" t="s">
+      <c r="A755" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="B755">
+      <c r="B755" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="756" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A756" s="1" t="s">
+      <c r="A756" s="3" t="s">
         <v>674</v>
       </c>
-      <c r="B756" t="s">
+      <c r="B756" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="757" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A757" s="1" t="s">
+      <c r="A757" s="3" t="s">
         <v>675</v>
       </c>
-      <c r="B757" t="s">
+      <c r="B757" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="758" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A758" s="1" t="s">
+      <c r="A758" s="3" t="s">
         <v>676</v>
       </c>
-      <c r="B758" t="s">
+      <c r="B758" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="759" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A759" s="1" t="s">
+      <c r="A759" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="B759" t="s">
+      <c r="B759" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="760" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A760" s="1" t="s">
+      <c r="A760" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="B760">
+      <c r="B760" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A761" s="1" t="s">
+      <c r="A761" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="B761">
+      <c r="B761" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="762" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A762" s="1" t="s">
+      <c r="A762" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="B762">
+      <c r="B762" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="763" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A763" s="1" t="s">
+      <c r="A763" s="3" t="s">
         <v>678</v>
       </c>
-      <c r="B763" t="s">
+      <c r="B763" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="764" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A764" s="1" t="s">
+      <c r="A764" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="B764" t="s">
+      <c r="B764" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="765" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A765" s="1" t="s">
+      <c r="A765" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="B765" t="s">
+      <c r="B765" s="4" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="766" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A766" t="s">
+      <c r="A766" s="4" t="s">
         <v>761</v>
       </c>
-      <c r="B766">
-        <v>25</v>
-      </c>
-      <c r="C766" t="s">
+      <c r="B766" s="4">
+        <v>25</v>
+      </c>
+      <c r="C766" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="767" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A767" t="s">
+      <c r="A767" s="4" t="s">
         <v>895</v>
       </c>
-      <c r="B767">
-        <v>25</v>
-      </c>
-      <c r="C767" t="s">
+      <c r="B767" s="4">
+        <v>25</v>
+      </c>
+      <c r="C767" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="768" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A768" t="s">
+      <c r="A768" s="4" t="s">
         <v>762</v>
       </c>
-      <c r="B768">
-        <v>25</v>
-      </c>
-      <c r="C768" t="s">
+      <c r="B768" s="4">
+        <v>25</v>
+      </c>
+      <c r="C768" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="769" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A769" t="s">
+      <c r="A769" s="4" t="s">
         <v>763</v>
       </c>
-      <c r="B769">
-        <v>25</v>
-      </c>
-      <c r="C769" t="s">
+      <c r="B769" s="4">
+        <v>25</v>
+      </c>
+      <c r="C769" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="770" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A770" t="s">
+      <c r="A770" s="4" t="s">
         <v>763</v>
       </c>
-      <c r="B770">
-        <v>25</v>
-      </c>
-      <c r="C770" t="s">
+      <c r="B770" s="4">
+        <v>25</v>
+      </c>
+      <c r="C770" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="771" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A771" t="s">
+      <c r="A771" s="4" t="s">
         <v>764</v>
       </c>
-      <c r="B771">
-        <v>25</v>
-      </c>
-      <c r="C771" t="s">
+      <c r="B771" s="4">
+        <v>25</v>
+      </c>
+      <c r="C771" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A772" s="1" t="s">
+      <c r="A772" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="B772">
+      <c r="B772" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="773" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A773" s="1" t="s">
+      <c r="A773" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="B773">
+      <c r="B773" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="774" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A774" t="s">
+      <c r="A774" s="4" t="s">
         <v>896</v>
       </c>
-      <c r="B774">
-        <v>25</v>
-      </c>
-      <c r="C774" t="s">
+      <c r="B774" s="4">
+        <v>25</v>
+      </c>
+      <c r="C774" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="775" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A775" t="s">
+      <c r="A775" s="4" t="s">
         <v>765</v>
       </c>
-      <c r="B775">
-        <v>25</v>
-      </c>
-      <c r="C775" t="s">
+      <c r="B775" s="4">
+        <v>25</v>
+      </c>
+      <c r="C775" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="776" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A776" t="s">
+      <c r="A776" s="4" t="s">
         <v>766</v>
       </c>
-      <c r="B776">
-        <v>25</v>
-      </c>
-      <c r="C776" t="s">
+      <c r="B776" s="4">
+        <v>25</v>
+      </c>
+      <c r="C776" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="777" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A777" t="s">
+      <c r="A777" s="4" t="s">
         <v>766</v>
       </c>
-      <c r="B777">
-        <v>25</v>
-      </c>
-      <c r="C777" t="s">
+      <c r="B777" s="4">
+        <v>25</v>
+      </c>
+      <c r="C777" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="778" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A778" t="s">
+      <c r="A778" s="4" t="s">
         <v>897</v>
       </c>
-      <c r="B778">
-        <v>25</v>
-      </c>
-      <c r="C778" t="s">
+      <c r="B778" s="4">
+        <v>25</v>
+      </c>
+      <c r="C778" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="779" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A779" t="s">
+      <c r="A779" s="4" t="s">
         <v>767</v>
       </c>
-      <c r="B779">
-        <v>25</v>
-      </c>
-      <c r="C779" t="s">
+      <c r="B779" s="4">
+        <v>25</v>
+      </c>
+      <c r="C779" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="780" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A780" t="s">
+      <c r="A780" s="4" t="s">
         <v>768</v>
       </c>
-      <c r="B780">
-        <v>25</v>
-      </c>
-      <c r="C780" t="s">
+      <c r="B780" s="4">
+        <v>25</v>
+      </c>
+      <c r="C780" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="781" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A781" t="s">
+      <c r="A781" s="4" t="s">
         <v>769</v>
       </c>
-      <c r="B781">
-        <v>25</v>
-      </c>
-      <c r="C781" t="s">
+      <c r="B781" s="4">
+        <v>25</v>
+      </c>
+      <c r="C781" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="782" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A782" t="s">
+      <c r="A782" s="4" t="s">
         <v>769</v>
       </c>
-      <c r="B782">
-        <v>25</v>
-      </c>
-      <c r="C782" t="s">
+      <c r="B782" s="4">
+        <v>25</v>
+      </c>
+      <c r="C782" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A783" t="s">
+      <c r="A783" s="4" t="s">
         <v>770</v>
       </c>
-      <c r="B783">
-        <v>25</v>
-      </c>
-      <c r="C783" t="s">
+      <c r="B783" s="4">
+        <v>25</v>
+      </c>
+      <c r="C783" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="784" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A784" t="s">
+      <c r="A784" s="4" t="s">
         <v>770</v>
       </c>
-      <c r="B784">
-        <v>25</v>
-      </c>
-      <c r="C784" t="s">
+      <c r="B784" s="4">
+        <v>25</v>
+      </c>
+      <c r="C784" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="785" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A785" t="s">
+      <c r="A785" s="4" t="s">
         <v>771</v>
       </c>
-      <c r="B785">
-        <v>25</v>
-      </c>
-      <c r="C785" t="s">
+      <c r="B785" s="4">
+        <v>25</v>
+      </c>
+      <c r="C785" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="786" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A786" t="s">
+      <c r="A786" s="4" t="s">
         <v>771</v>
       </c>
-      <c r="B786">
-        <v>25</v>
-      </c>
-      <c r="C786" t="s">
+      <c r="B786" s="4">
+        <v>25</v>
+      </c>
+      <c r="C786" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="787" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A787" t="s">
+      <c r="A787" s="4" t="s">
         <v>772</v>
       </c>
-      <c r="B787">
-        <v>25</v>
-      </c>
-      <c r="C787" t="s">
+      <c r="B787" s="4">
+        <v>25</v>
+      </c>
+      <c r="C787" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="788" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A788" t="s">
+      <c r="A788" s="4" t="s">
         <v>772</v>
       </c>
-      <c r="B788">
-        <v>25</v>
-      </c>
-      <c r="C788" t="s">
+      <c r="B788" s="4">
+        <v>25</v>
+      </c>
+      <c r="C788" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="789" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A789" t="s">
+      <c r="A789" s="4" t="s">
         <v>898</v>
       </c>
-      <c r="B789">
-        <v>25</v>
-      </c>
-      <c r="C789" t="s">
+      <c r="B789" s="4">
+        <v>25</v>
+      </c>
+      <c r="C789" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="790" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A790" t="s">
+      <c r="A790" s="4" t="s">
         <v>773</v>
       </c>
-      <c r="B790">
-        <v>25</v>
-      </c>
-      <c r="C790" t="s">
+      <c r="B790" s="4">
+        <v>25</v>
+      </c>
+      <c r="C790" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="791" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A791" t="s">
+      <c r="A791" s="4" t="s">
         <v>774</v>
       </c>
-      <c r="B791">
-        <v>25</v>
-      </c>
-      <c r="C791" t="s">
+      <c r="B791" s="4">
+        <v>25</v>
+      </c>
+      <c r="C791" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="792" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A792" t="s">
+      <c r="A792" s="4" t="s">
         <v>775</v>
       </c>
-      <c r="B792">
-        <v>25</v>
-      </c>
-      <c r="C792" t="s">
+      <c r="B792" s="4">
+        <v>25</v>
+      </c>
+      <c r="C792" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="793" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A793" t="s">
+      <c r="A793" s="4" t="s">
         <v>775</v>
       </c>
-      <c r="B793">
-        <v>25</v>
-      </c>
-      <c r="C793" t="s">
+      <c r="B793" s="4">
+        <v>25</v>
+      </c>
+      <c r="C793" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A794" t="s">
+      <c r="A794" s="4" t="s">
         <v>776</v>
       </c>
-      <c r="B794">
-        <v>25</v>
-      </c>
-      <c r="C794" t="s">
+      <c r="B794" s="4">
+        <v>25</v>
+      </c>
+      <c r="C794" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="795" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A795" t="s">
+      <c r="A795" s="4" t="s">
         <v>776</v>
       </c>
-      <c r="B795">
-        <v>25</v>
-      </c>
-      <c r="C795" t="s">
+      <c r="B795" s="4">
+        <v>25</v>
+      </c>
+      <c r="C795" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="796" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A796" t="s">
+      <c r="A796" s="4" t="s">
         <v>777</v>
       </c>
-      <c r="B796">
-        <v>25</v>
-      </c>
-      <c r="C796" t="s">
+      <c r="B796" s="4">
+        <v>25</v>
+      </c>
+      <c r="C796" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="797" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A797" t="s">
+      <c r="A797" s="4" t="s">
         <v>777</v>
       </c>
-      <c r="B797">
-        <v>25</v>
-      </c>
-      <c r="C797" t="s">
+      <c r="B797" s="4">
+        <v>25</v>
+      </c>
+      <c r="C797" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="798" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A798" t="s">
+      <c r="A798" s="4" t="s">
         <v>778</v>
       </c>
-      <c r="B798">
-        <v>25</v>
-      </c>
-      <c r="C798" t="s">
+      <c r="B798" s="4">
+        <v>25</v>
+      </c>
+      <c r="C798" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="799" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A799" t="s">
+      <c r="A799" s="4" t="s">
         <v>778</v>
       </c>
-      <c r="B799">
-        <v>25</v>
-      </c>
-      <c r="C799" t="s">
+      <c r="B799" s="4">
+        <v>25</v>
+      </c>
+      <c r="C799" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="800" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A800" t="s">
+      <c r="A800" s="4" t="s">
         <v>779</v>
       </c>
-      <c r="B800">
-        <v>25</v>
-      </c>
-      <c r="C800" t="s">
+      <c r="B800" s="4">
+        <v>25</v>
+      </c>
+      <c r="C800" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="801" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A801" t="s">
+      <c r="A801" s="4" t="s">
         <v>779</v>
       </c>
-      <c r="B801">
-        <v>25</v>
-      </c>
-      <c r="C801" t="s">
+      <c r="B801" s="4">
+        <v>25</v>
+      </c>
+      <c r="C801" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="802" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A802" t="s">
+      <c r="A802" s="4" t="s">
         <v>780</v>
       </c>
-      <c r="B802">
-        <v>25</v>
-      </c>
-      <c r="C802" t="s">
+      <c r="B802" s="4">
+        <v>25</v>
+      </c>
+      <c r="C802" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="803" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A803" t="s">
+      <c r="A803" s="4" t="s">
         <v>780</v>
       </c>
-      <c r="B803">
-        <v>25</v>
-      </c>
-      <c r="C803" t="s">
+      <c r="B803" s="4">
+        <v>25</v>
+      </c>
+      <c r="C803" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="804" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A804" t="s">
+      <c r="A804" s="4" t="s">
         <v>781</v>
       </c>
-      <c r="B804">
-        <v>25</v>
-      </c>
-      <c r="C804" t="s">
+      <c r="B804" s="4">
+        <v>25</v>
+      </c>
+      <c r="C804" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A805" t="s">
+      <c r="A805" s="4" t="s">
         <v>781</v>
       </c>
-      <c r="B805">
-        <v>25</v>
-      </c>
-      <c r="C805" t="s">
+      <c r="B805" s="4">
+        <v>25</v>
+      </c>
+      <c r="C805" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="806" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A806" t="s">
+      <c r="A806" s="4" t="s">
         <v>782</v>
       </c>
-      <c r="B806">
-        <v>25</v>
-      </c>
-      <c r="C806" t="s">
+      <c r="B806" s="4">
+        <v>25</v>
+      </c>
+      <c r="C806" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="807" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A807" t="s">
+      <c r="A807" s="4" t="s">
         <v>782</v>
       </c>
-      <c r="B807">
-        <v>25</v>
-      </c>
-      <c r="C807" t="s">
+      <c r="B807" s="4">
+        <v>25</v>
+      </c>
+      <c r="C807" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="808" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A808" s="1" t="s">
+      <c r="A808" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="B808">
+      <c r="B808" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="809" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A809" s="1" t="s">
+      <c r="A809" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="B809">
+      <c r="B809" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="810" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A810" s="1" t="s">
+      <c r="A810" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="B810">
+      <c r="B810" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="811" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A811" s="1" t="s">
+      <c r="A811" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="B811">
+      <c r="B811" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="812" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A812" s="1" t="s">
+      <c r="A812" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="B812">
+      <c r="B812" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="813" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A813" s="1" t="s">
+      <c r="A813" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="B813">
+      <c r="B813" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="814" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A814" s="1" t="s">
+      <c r="A814" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="B814">
+      <c r="B814" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="815" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A815" s="1" t="s">
+      <c r="A815" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="B815">
+      <c r="B815" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A816" s="1" t="s">
+      <c r="A816" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="B816">
+      <c r="B816" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="817" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A817" s="1" t="s">
+      <c r="A817" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="B817">
+      <c r="B817" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="818" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A818" t="s">
+      <c r="A818" s="4" t="s">
         <v>783</v>
       </c>
-      <c r="B818">
-        <v>25</v>
-      </c>
-      <c r="C818" t="s">
+      <c r="B818" s="4">
+        <v>25</v>
+      </c>
+      <c r="C818" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="819" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A819" t="s">
+      <c r="A819" s="4" t="s">
         <v>783</v>
       </c>
-      <c r="B819">
-        <v>25</v>
-      </c>
-      <c r="C819" t="s">
+      <c r="B819" s="4">
+        <v>25</v>
+      </c>
+      <c r="C819" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="820" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A820" t="s">
+      <c r="A820" s="4" t="s">
         <v>784</v>
       </c>
-      <c r="B820">
-        <v>25</v>
-      </c>
-      <c r="C820" t="s">
+      <c r="B820" s="4">
+        <v>25</v>
+      </c>
+      <c r="C820" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="821" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A821" t="s">
+      <c r="A821" s="4" t="s">
         <v>784</v>
       </c>
-      <c r="B821">
-        <v>25</v>
-      </c>
-      <c r="C821" t="s">
+      <c r="B821" s="4">
+        <v>25</v>
+      </c>
+      <c r="C821" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="822" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A822" t="s">
+      <c r="A822" s="4" t="s">
         <v>785</v>
       </c>
-      <c r="B822">
-        <v>25</v>
-      </c>
-      <c r="C822" t="s">
+      <c r="B822" s="4">
+        <v>25</v>
+      </c>
+      <c r="C822" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="823" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A823" t="s">
+      <c r="A823" s="4" t="s">
         <v>899</v>
       </c>
-      <c r="B823">
-        <v>25</v>
-      </c>
-      <c r="C823" t="s">
+      <c r="B823" s="4">
+        <v>25</v>
+      </c>
+      <c r="C823" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="824" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A824" t="s">
+      <c r="A824" s="4" t="s">
         <v>900</v>
       </c>
-      <c r="B824">
-        <v>25</v>
-      </c>
-      <c r="C824" t="s">
+      <c r="B824" s="4">
+        <v>25</v>
+      </c>
+      <c r="C824" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="825" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A825" t="s">
+      <c r="A825" s="4" t="s">
         <v>901</v>
       </c>
-      <c r="B825">
-        <v>25</v>
-      </c>
-      <c r="C825" t="s">
+      <c r="B825" s="4">
+        <v>25</v>
+      </c>
+      <c r="C825" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="826" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A826" t="s">
+      <c r="A826" s="4" t="s">
         <v>786</v>
       </c>
-      <c r="B826">
-        <v>25</v>
-      </c>
-      <c r="C826" t="s">
+      <c r="B826" s="4">
+        <v>25</v>
+      </c>
+      <c r="C826" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A827" t="s">
+      <c r="A827" s="4" t="s">
         <v>902</v>
       </c>
-      <c r="B827">
-        <v>25</v>
-      </c>
-      <c r="C827" t="s">
+      <c r="B827" s="4">
+        <v>25</v>
+      </c>
+      <c r="C827" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="828" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A828" t="s">
+      <c r="A828" s="4" t="s">
         <v>903</v>
       </c>
-      <c r="B828">
-        <v>25</v>
-      </c>
-      <c r="C828" t="s">
+      <c r="B828" s="4">
+        <v>25</v>
+      </c>
+      <c r="C828" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="829" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A829" s="1" t="s">
+      <c r="A829" s="3" t="s">
         <v>613</v>
       </c>
-      <c r="B829">
+      <c r="B829" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="830" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A830" t="s">
+      <c r="A830" s="4" t="s">
         <v>787</v>
       </c>
-      <c r="B830">
-        <v>25</v>
-      </c>
-      <c r="C830" t="s">
+      <c r="B830" s="4">
+        <v>25</v>
+      </c>
+      <c r="C830" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="831" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A831" t="s">
+      <c r="A831" s="4" t="s">
         <v>787</v>
       </c>
-      <c r="B831">
-        <v>25</v>
-      </c>
-      <c r="C831" t="s">
+      <c r="B831" s="4">
+        <v>25</v>
+      </c>
+      <c r="C831" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="832" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A832" s="1" t="s">
+      <c r="A832" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="B832">
+      <c r="B832" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="833" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A833" t="s">
+      <c r="A833" s="4" t="s">
         <v>788</v>
       </c>
-      <c r="B833">
-        <v>25</v>
-      </c>
-      <c r="C833" t="s">
+      <c r="B833" s="4">
+        <v>25</v>
+      </c>
+      <c r="C833" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="834" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A834" t="s">
+      <c r="A834" s="4" t="s">
         <v>789</v>
       </c>
-      <c r="B834">
-        <v>25</v>
-      </c>
-      <c r="C834" t="s">
+      <c r="B834" s="4">
+        <v>25</v>
+      </c>
+      <c r="C834" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="835" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A835" s="1" t="s">
+      <c r="A835" s="3" t="s">
         <v>615</v>
       </c>
-      <c r="B835">
+      <c r="B835" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="836" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A836" t="s">
+      <c r="A836" s="4" t="s">
         <v>790</v>
       </c>
-      <c r="B836">
-        <v>25</v>
-      </c>
-      <c r="C836" t="s">
+      <c r="B836" s="4">
+        <v>25</v>
+      </c>
+      <c r="C836" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="837" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A837" t="s">
+      <c r="A837" s="4" t="s">
         <v>790</v>
       </c>
-      <c r="B837">
-        <v>25</v>
-      </c>
-      <c r="C837" t="s">
+      <c r="B837" s="4">
+        <v>25</v>
+      </c>
+      <c r="C837" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A838" t="s">
+      <c r="A838" s="4" t="s">
         <v>791</v>
       </c>
-      <c r="B838">
-        <v>25</v>
-      </c>
-      <c r="C838" t="s">
+      <c r="B838" s="4">
+        <v>25</v>
+      </c>
+      <c r="C838" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="839" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A839" t="s">
+      <c r="A839" s="4" t="s">
         <v>791</v>
       </c>
-      <c r="B839">
-        <v>25</v>
-      </c>
-      <c r="C839" t="s">
+      <c r="B839" s="4">
+        <v>25</v>
+      </c>
+      <c r="C839" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="840" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A840" s="1" t="s">
+      <c r="A840" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="B840">
+      <c r="B840" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="841" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A841" s="1" t="s">
+      <c r="A841" s="3" t="s">
         <v>617</v>
       </c>
-      <c r="B841">
+      <c r="B841" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="842" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A842" t="s">
+      <c r="A842" s="4" t="s">
         <v>792</v>
       </c>
-      <c r="B842">
-        <v>25</v>
-      </c>
-      <c r="C842" t="s">
+      <c r="B842" s="4">
+        <v>25</v>
+      </c>
+      <c r="C842" s="4" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="843" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A843" t="s">
+      <c r="A843" s="4" t="s">
         <v>792</v>
       </c>
-      <c r="B843">
-        <v>25</v>
-      </c>
-      <c r="C843" t="s">
+      <c r="B843" s="4">
+        <v>25</v>
+      </c>
+      <c r="C843" s="4" t="s">
         <v>861</v>
       </c>
     </row>
     <row r="844" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A844" s="1" t="s">
+      <c r="A844" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="B844">
+      <c r="B844" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="845" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A845" s="1" t="s">
+      <c r="A845" s="3" t="s">
         <v>632</v>
       </c>
-      <c r="B845">
+      <c r="B845" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="846" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A846" s="1" t="s">
+      <c r="A846" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="B846">
+      <c r="B846" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="847" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A847" s="1" t="s">
+      <c r="A847" s="3" t="s">
         <v>633</v>
       </c>
-      <c r="B847">
+      <c r="B847" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="848" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A848" s="1" t="s">
+      <c r="A848" s="3" t="s">
         <v>619</v>
       </c>
-      <c r="B848">
+      <c r="B848" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="849" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A849" s="1" t="s">
+      <c r="A849" s="3" t="s">
         <v>620</v>
       </c>
-      <c r="B849">
+      <c r="B849" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="850" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A850" s="1" t="s">
+      <c r="A850" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="B850">
+      <c r="B850" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="851" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A851" s="1" t="s">
+      <c r="A851" s="3" t="s">
         <v>622</v>
       </c>
-      <c r="B851">
+      <c r="B851" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="852" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A852" s="1" t="s">
+      <c r="A852" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="B852">
+      <c r="B852" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="853" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A853" s="1" t="s">
+      <c r="A853" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="B853">
+      <c r="B853" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="854" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A854" s="1" t="s">
+      <c r="A854" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="B854">
+      <c r="B854" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="855" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A855" s="1" t="s">
+      <c r="A855" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="B855">
+      <c r="B855" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="856" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A856" s="1" t="s">
+      <c r="A856" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="B856">
+      <c r="B856" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="857" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A857" s="1" t="s">
+      <c r="A857" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="B857">
+      <c r="B857" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="858" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A858" s="1" t="s">
+      <c r="A858" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="B858">
+      <c r="B858" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="859" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A859" s="1" t="s">
+      <c r="A859" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="B859">
+      <c r="B859" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="860" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A860" s="1" t="s">
+      <c r="A860" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="B860">
+      <c r="B860" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="861" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A861" s="1" t="s">
+      <c r="A861" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="B861">
+      <c r="B861" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="862" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A862" s="1" t="s">
+      <c r="A862" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="B862">
+      <c r="B862" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="863" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A863" s="1" t="s">
+      <c r="A863" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="B863">
+      <c r="B863" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="864" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A864" s="1" t="s">
+      <c r="A864" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="B864">
+      <c r="B864" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="865" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A865" s="1" t="s">
+      <c r="A865" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="B865">
+      <c r="B865" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="866" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A866" s="1" t="s">
+      <c r="A866" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="B866">
+      <c r="B866" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="867" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A867" s="1" t="s">
+      <c r="A867" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="B867">
+      <c r="B867" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="868" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A868" s="1" t="s">
+      <c r="A868" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="B868">
+      <c r="B868" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="869" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A869" s="1" t="s">
+      <c r="A869" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="B869">
+      <c r="B869" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="870" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A870" s="1" t="s">
+      <c r="A870" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="B870">
+      <c r="B870" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A871" s="1" t="s">
+      <c r="A871" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="B871">
+      <c r="B871" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="872" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A872" s="1" t="s">
+      <c r="A872" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="B872">
+      <c r="B872" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="873" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A873" s="1" t="s">
+      <c r="A873" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="B873">
+      <c r="B873" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="874" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A874" s="1" t="s">
+      <c r="A874" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="B874">
+      <c r="B874" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="875" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A875" s="1" t="s">
+      <c r="A875" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="B875">
+      <c r="B875" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="876" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A876" s="1" t="s">
+      <c r="A876" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="B876">
+      <c r="B876" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="877" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A877" s="1" t="s">
+      <c r="A877" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="B877">
+      <c r="B877" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="878" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A878" s="1" t="s">
+      <c r="A878" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="B878">
+      <c r="B878" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="879" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A879" s="1" t="s">
+      <c r="A879" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="B879">
+      <c r="B879" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="880" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A880" t="s">
+      <c r="A880" s="4" t="s">
         <v>829</v>
       </c>
-      <c r="B880">
-        <v>25</v>
-      </c>
-      <c r="C880" t="s">
+      <c r="B880" s="4">
+        <v>25</v>
+      </c>
+      <c r="C880" s="4" t="s">
         <v>830</v>
       </c>
     </row>
     <row r="881" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A881" s="1" t="s">
+      <c r="A881" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="B881">
+      <c r="B881" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A882" t="s">
+      <c r="A882" s="4" t="s">
         <v>831</v>
       </c>
-      <c r="B882">
-        <v>25</v>
-      </c>
-      <c r="C882" t="s">
+      <c r="B882" s="4">
+        <v>25</v>
+      </c>
+      <c r="C882" s="4" t="s">
         <v>830</v>
       </c>
     </row>
     <row r="883" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A883" s="1" t="s">
+      <c r="A883" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="B883">
+      <c r="B883" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="884" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A884" t="s">
+      <c r="A884" s="4" t="s">
         <v>832</v>
       </c>
-      <c r="B884">
-        <v>25</v>
-      </c>
-      <c r="C884" t="s">
+      <c r="B884" s="4">
+        <v>25</v>
+      </c>
+      <c r="C884" s="4" t="s">
         <v>830</v>
       </c>
     </row>
     <row r="885" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A885" s="1" t="s">
+      <c r="A885" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="B885">
+      <c r="B885" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="886" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A886" t="s">
+      <c r="A886" s="4" t="s">
         <v>833</v>
       </c>
-      <c r="B886">
-        <v>25</v>
-      </c>
-      <c r="C886" t="s">
+      <c r="B886" s="4">
+        <v>25</v>
+      </c>
+      <c r="C886" s="4" t="s">
         <v>830</v>
       </c>
     </row>
     <row r="887" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A887" s="1" t="s">
+      <c r="A887" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="B887">
+      <c r="B887" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="888" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A888" t="s">
+      <c r="A888" s="4" t="s">
         <v>834</v>
       </c>
-      <c r="B888">
-        <v>25</v>
-      </c>
-      <c r="C888" t="s">
+      <c r="B888" s="4">
+        <v>25</v>
+      </c>
+      <c r="C888" s="4" t="s">
         <v>830</v>
       </c>
     </row>
     <row r="889" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A889" s="1" t="s">
+      <c r="A889" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="B889">
+      <c r="B889" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="890" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A890" s="1" t="s">
+      <c r="A890" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="B890">
+      <c r="B890" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="891" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A891" s="1" t="s">
+      <c r="A891" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="B891">
+      <c r="B891" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="892" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A892" s="1" t="s">
+      <c r="A892" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="B892">
+      <c r="B892" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A893" s="1" t="s">
+      <c r="A893" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="B893">
+      <c r="B893" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="894" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A894" s="1" t="s">
+      <c r="A894" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="B894">
+      <c r="B894" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="895" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A895" s="1" t="s">
+      <c r="A895" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="B895">
+      <c r="B895" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="896" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A896" s="1" t="s">
+      <c r="A896" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="B896">
+      <c r="B896" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="897" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A897" s="1" t="s">
+      <c r="A897" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="B897">
+      <c r="B897" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="898" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A898" s="1" t="s">
+      <c r="A898" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="B898">
+      <c r="B898" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="899" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A899" s="1" t="s">
+      <c r="A899" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="B899">
+      <c r="B899" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="900" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A900" s="1" t="s">
+      <c r="A900" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="B900">
+      <c r="B900" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="901" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A901" s="1" t="s">
+      <c r="A901" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="B901">
+      <c r="B901" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="902" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A902" s="1" t="s">
+      <c r="A902" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="B902">
+      <c r="B902" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="903" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A903" t="s">
+      <c r="A903" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="B903">
+      <c r="B903" s="4">
         <v>10</v>
       </c>
-      <c r="C903" t="s">
+      <c r="C903" s="4" t="s">
         <v>852</v>
       </c>
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A904" s="1" t="s">
+      <c r="A904" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="B904">
+      <c r="B904" s="4">
         <v>25</v>
       </c>
     </row>
     <row r="905" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A905" t="s">
+      <c r="A905" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="B905">
+      <c r="B905" s="4">
         <v>10</v>
       </c>
-      <c r="C905" t="s">
+      <c r="C905" s="4" t="s">
         <v>852</v>
       </c>
     </row>
